--- a/ru/downloads/data-excel/15.4.1.xlsx
+++ b/ru/downloads/data-excel/15.4.1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -191,7 +191,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -237,6 +237,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -543,7 +546,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="41.140625" customWidth="1"/>
@@ -554,7 +557,7 @@
     <col min="6" max="8" width="9.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -571,7 +574,7 @@
       <c r="H1" s="4"/>
       <c r="I1" s="5"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
         <v>9</v>
       </c>
@@ -588,7 +591,7 @@
       <c r="H2" s="8"/>
       <c r="I2" s="9"/>
     </row>
-    <row r="3" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="7"/>
       <c r="C3" s="8"/>
@@ -599,7 +602,7 @@
       <c r="H3" s="8"/>
       <c r="I3" s="9"/>
     </row>
-    <row r="4" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>0</v>
       </c>
@@ -642,8 +645,11 @@
       <c r="N4" s="12">
         <v>2023</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O4" s="18">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>7</v>
       </c>
@@ -686,8 +692,11 @@
       <c r="N5" s="14">
         <v>6.18</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O5" s="14">
+        <v>6.92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -699,7 +708,7 @@
       <c r="I6" s="5"/>
       <c r="K6" s="15"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -711,7 +720,7 @@
       <c r="I7" s="5"/>
       <c r="K7" s="16"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
@@ -722,7 +731,7 @@
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -733,7 +742,7 @@
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -744,7 +753,7 @@
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
